--- a/流程不同步，错误修复记录.xlsx
+++ b/流程不同步，错误修复记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\szy\Desktop\xinji\AuxiliaryMaterialsMulti-slotRobt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1DAF8D-3AF0-4864-A113-309707575D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{195382A6-55B6-49A1-A73C-508E66ACBD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -78,6 +78,97 @@
   </si>
   <si>
     <t>修改决定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>queryMatchedAvailableWire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outcome_routing 把 empty 与 single 都路由到同一判定节点 checkMatchedWireExists，靠判定再分流。逻辑可行，但「空结果」与「正常单行」在路由层未区分，排障时不直观。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可接受；建议在 catalog 注明 empty 语义，或单独给 empty 一个提示分支。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">operator </t>
+  </si>
+  <si>
+    <t xml:space="preserve">operator </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>归还成功后的物理动作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>流程图在 归还提交成功 后还有「开归还格口 → 放入焊丝 → 关门」再进入领用；但 flow-sql-map 的 node_order 未建模这些开门/关门/等待关闭节点，直接从 checkSubmitWireReturnSuccess 跳到 queryWireByLotNo。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若需要工具/系统真正驱动归还格口仓门，应在 map 中补 openReturnSlot / closeReturnSlotDoor / isAllSlotDoorsClosed 等节点（可复用打开格口流程的循环）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>showRemainingQtyWrongHint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>流程图为「配额&gt;500 → 提示数量有误 → 返回重输数量」（回环）；map 未建模回环，验证版按失败终止处理。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若要支持重输，map 应将该提示节点 success 路由回 inputRemainingQty。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>queryProductByLotNo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SUM/MAX 聚合查询无匹配行时仍返回一行但 qty/step 为空，必须靠 checkProductInfoExists 判空，否则会把空值当成功提交领用。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已正确建模为 all_fields_not_empty；提醒实现端务必判空。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果返回N/A，认为是错误的；无法继续</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Error添加提示，其他保持不变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>补充结点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>补齐几点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这只是提醒</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -417,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="30.7265625" customWidth="1"/>
@@ -446,7 +537,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="182" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="42" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -461,6 +552,89 @@
       </c>
       <c r="E2" s="3" t="s">
         <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
